--- a/report-2026-06-07.xlsx
+++ b/report-2026-06-07.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="1325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1329">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-07T13:41:51+05:30</t>
+    <t>Generated 2026-06-07T13:52:09+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-07T13:39:51+05:30 (2m0s ago)</t>
+    <t>2026-06-07T13:50:09+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3985,10 +3985,22 @@
     <t>13:39:51.352</t>
   </si>
   <si>
+    <t>2026-06-07T13:44:52.5859098+05:30</t>
+  </si>
+  <si>
+    <t>13:44:52.585</t>
+  </si>
+  <si>
+    <t>2026-06-07T13:50:09.3956596+05:30</t>
+  </si>
+  <si>
+    <t>13:50:09.395</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-07T13:41:51+05:30</t>
+    <t>2026-06-07T13:52:09+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4588,7 +4600,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-07 13:39:36</t>
+          <t>2026-06-07 13:49:54</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4598,12 +4610,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-07 13:39:36</t>
+          <t>2026-06-07 13:49:54</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>17h 11m 14s</t>
+          <t>17h 18m 8s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4613,7 +4625,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:41:51</t>
+          <t>13:52:09</t>
         </is>
       </c>
     </row>
@@ -4670,17 +4682,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>121564.5</t>
+          <t>124129.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4705,12 +4717,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-07 13:39:36</t>
+          <t>2026-06-07 13:49:54</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17h 9m 47s</t>
+          <t>17h 17m 28s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4720,7 +4732,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:41:51</t>
+          <t>13:52:09</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4851,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07T13:39:51.3523919+05:30</t>
+          <t>2026-06-07T13:50:09.3956596+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4849,7 +4861,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:39:51.352</t>
+          <t>13:50:09.395</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -39060,18 +39072,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" s="4">
+        <v>636</v>
+      </c>
+      <c r="B653" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C653" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D653" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E653" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F653" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G653" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H653" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I653" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J653" s="4">
+        <v>0</v>
+      </c>
+      <c r="K653" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L653" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="654">
-      <c r="A654" t="s">
-        <v>1322</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D654" t="s">
+      <c r="A654" s="4">
+        <v>637</v>
+      </c>
+      <c r="B654" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="E654">
-        <v>635</v>
+      <c r="C654" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D654" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E654" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F654" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G654" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H654" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I654" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J654" s="4">
+        <v>0</v>
+      </c>
+      <c r="K654" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L654" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D656" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E656">
+        <v>637</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-07.xlsx
+++ b/report-2026-06-07.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="1333">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-07T13:52:09+05:30</t>
+    <t>Generated 2026-06-07T14:02:13+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-07T13:50:09+05:30 (2m0s ago)</t>
+    <t>2026-06-07T14:00:13+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3997,10 +3997,22 @@
     <t>13:50:09.395</t>
   </si>
   <si>
+    <t>2026-06-07T13:55:10.6595358+05:30</t>
+  </si>
+  <si>
+    <t>13:55:10.659</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:00:13.1036319+05:30</t>
+  </si>
+  <si>
+    <t>14:00:13.103</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-07T13:52:09+05:30</t>
+    <t>2026-06-07T14:02:13+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4555,7 +4567,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.61</t>
+          <t>10.0.62</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4595,12 +4607,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 13s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-07 13:49:54</t>
+          <t>2026-06-07 13:59:59</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4610,12 +4622,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-07 13:49:54</t>
+          <t>2026-06-07 13:59:59</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>17h 18m 8s</t>
+          <t>17h 26m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4625,7 +4637,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>13:52:09</t>
+          <t>14:02:13</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.61</t>
+          <t>10.0.62</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4682,17 +4694,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>124129.9</t>
+          <t>118710.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>891</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -4702,7 +4714,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -4717,12 +4729,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-07 13:49:54</t>
+          <t>2026-06-07 13:59:59</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17h 17m 28s</t>
+          <t>17h 24m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4732,7 +4744,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>13:52:09</t>
+          <t>14:02:13</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4863,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07T13:50:09.3956596+05:30</t>
+          <t>2026-06-07T14:00:13.1036319+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4861,7 +4873,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:50:09.395</t>
+          <t>14:00:13.103</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -39148,18 +39160,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" s="4">
+        <v>638</v>
+      </c>
+      <c r="B655" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C655" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D655" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E655" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F655" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G655" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H655" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I655" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J655" s="4">
+        <v>0</v>
+      </c>
+      <c r="K655" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L655" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="656">
-      <c r="A656" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D656" t="s">
+      <c r="A656" s="4">
+        <v>639</v>
+      </c>
+      <c r="B656" s="4" t="s">
         <v>1328</v>
       </c>
-      <c r="E656">
-        <v>637</v>
+      <c r="C656" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D656" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E656" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F656" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G656" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H656" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I656" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J656" s="4">
+        <v>0</v>
+      </c>
+      <c r="K656" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L656" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D658" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E658">
+        <v>639</v>
       </c>
     </row>
   </sheetData>
